--- a/java-projects/maven/maven-projects/aggregator/notes.xlsx
+++ b/java-projects/maven/maven-projects/aggregator/notes.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="27510"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10913"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/workspace/parent/notes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/workspace_intellij_practise/parent-java/java-projects/maven/maven-projects/aggregator/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8878A7BC-334B-314C-BE63-C353276E3E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="700" windowWidth="28680" windowHeight="17420" tabRatio="500"/>
+    <workbookView xWindow="1000" yWindow="2440" windowWidth="28680" windowHeight="17420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="practise" sheetId="4" r:id="rId1"/>
@@ -22,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">leetcode!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">practise!$A$1:$C$1</definedName>
   </definedNames>
-  <calcPr calcId="150000" concurrentCalc="0"/>
+  <calcPr calcId="150000"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -400,7 +401,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -459,6 +460,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -726,11 +730,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="33.5" customWidth="1"/>
+    <col min="3" max="3" width="57.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -750,13 +754,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1"/>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -794,13 +798,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1"/>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1647,13 +1651,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1"/>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
